--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -673,211 +673,211 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>3001</v>
+        <v>2010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event.Moving</t>
+          <t>Ability.Gun</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>事件：正在移动</t>
+          <t>枪械</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event.Dodging</t>
+          <t>Event.Moving</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>事件：正在闪避</t>
+          <t>事件：正在移动</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event.Attacking</t>
+          <t>Event.Dodging</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>事件：正在攻击</t>
+          <t>事件：正在闪避</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>4001</v>
+        <v>3003</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>State.Buff</t>
+          <t>Event.Attacking</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>状态：正向增益</t>
+          <t>事件：正在攻击</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State.Debuff</t>
+          <t>State.Buff</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>状态：负面增益</t>
+          <t>状态：正向增益</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>5001</v>
+        <v>4002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guide.Type1</t>
+          <t>State.Debuff</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新手引导：类型1</t>
+          <t>状态：负面增益</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Guide.Type2</t>
+          <t>Guide.Type1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新手引导：类型2</t>
+          <t>新手引导：类型1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Guide.Type3</t>
+          <t>Guide.Type2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新手引导：类型3</t>
+          <t>新手引导：类型2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1000000</v>
+        <v>5003</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faction</t>
+          <t>Guide.Type3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>阵营描述标签</t>
+          <t>新手引导：类型3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>4001001</v>
+        <v>1000000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>State.Buff.BulkUp</t>
+          <t>Faction</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>霸体</t>
+          <t>阵营描述标签</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>4001002</v>
+        <v>2010002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>State.Buff.SpeedUp</t>
+          <t>Ability.Gun.Shoot</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>状态：移速增加</t>
+          <t>射击</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>4001003</v>
+        <v>4001001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>State.Buff.SpCosting</t>
+          <t>State.Buff.BulkUp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>状态：耐力消耗中</t>
+          <t>霸体</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>4001006</v>
+        <v>4001002</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ability.Gun.Shoot</t>
+          <t>State.Buff.SpeedUp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>状态：移速增加</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>4001007</v>
+        <v>4001003</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ability.Gun</t>
+          <t>State.Buff.SpCosting</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>枪械</t>
+          <t>状态：耐力消耗中</t>
         </is>
       </c>
     </row>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19" customWidth="1" min="3" max="3"/>
@@ -673,226 +673,256 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ability.Gun</t>
+          <t>Ability.Magic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>枪械</t>
+          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>3001</v>
+        <v>2009</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event.Moving</t>
+          <t>Ability.Magic.Boom</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>事件：正在移动</t>
+          <t>爆弹</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>3002</v>
+        <v>2010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event.Dodging</t>
+          <t>Ability.Gun</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>事件：正在闪避</t>
+          <t>枪械</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event.Attacking</t>
+          <t>Event.Moving</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>事件：正在攻击</t>
+          <t>事件：正在移动</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>4001</v>
+        <v>3002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State.Buff</t>
+          <t>Event.Dodging</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>状态：正向增益</t>
+          <t>事件：正在闪避</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>4002</v>
+        <v>3003</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>State.Debuff</t>
+          <t>Event.Attacking</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>状态：负面增益</t>
+          <t>事件：正在攻击</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>5001</v>
+        <v>4001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Guide.Type1</t>
+          <t>State.Buff</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新手引导：类型1</t>
+          <t>状态：正向增益</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>5002</v>
+        <v>4002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Guide.Type2</t>
+          <t>State.Debuff</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新手引导：类型2</t>
+          <t>状态：负面增益</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Guide.Type3</t>
+          <t>Guide.Type1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>新手引导：类型3</t>
+          <t>新手引导：类型1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1000000</v>
+        <v>5002</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faction</t>
+          <t>Guide.Type2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>阵营描述标签</t>
+          <t>新手引导：类型2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>2010002</v>
+        <v>5003</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ability.Gun.Shoot</t>
+          <t>Guide.Type3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>新手引导：类型3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>4001001</v>
+        <v>1000000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>State.Buff.BulkUp</t>
+          <t>Faction</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>霸体</t>
+          <t>阵营描述标签</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>4001002</v>
+        <v>2010001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>State.Buff.SpeedUp</t>
+          <t>Ability.Gun.Aim</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>状态：移速增加</t>
+          <t>瞄准</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>4001003</v>
+        <v>2010002</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>State.Buff.SpCosting</t>
+          <t>Ability.Gun.Shoot</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>状态：耐力消耗中</t>
+          <t>射击</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>4001008</v>
+        <v>4001001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ability.Gun.Aim</t>
+          <t>State.Buff.BulkUp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>瞄准</t>
+          <t>霸体</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>4001002</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>State.Buff.SpeedUp</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>状态：移速增加</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>4001003</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>State.Buff.SpCosting</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>状态：耐力消耗中</t>
         </is>
       </c>
     </row>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19" customWidth="1" min="3" max="3"/>
@@ -883,44 +883,59 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>4001001</v>
+        <v>2010003</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>State.Buff.BulkUp</t>
+          <t>Ability.Gun.SuperShoot</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>霸体</t>
+          <t>强力射击</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>4001002</v>
+        <v>4001001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>State.Buff.SpeedUp</t>
+          <t>State.Buff.BulkUp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>状态：移速增加</t>
+          <t>霸体</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
+        <v>4001002</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>State.Buff.SpeedUp</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>状态：移速增加</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
         <v>4001003</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>State.Buff.SpCosting</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>状态：耐力消耗中</t>
         </is>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19" customWidth="1" min="3" max="3"/>
@@ -553,391 +553,436 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>1001</v>
+        <v>600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faction.Player</t>
+          <t>Cooldown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>玩家阵营</t>
+          <t>冷却</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Faction.Enemy</t>
+          <t>Faction.Player</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>敌人阵营</t>
+          <t>玩家阵营</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>2001</v>
+        <v>1002</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ability.Die</t>
+          <t>Faction.Enemy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>技能：死亡</t>
+          <t>敌人阵营</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ability.Move</t>
+          <t>Ability.Die</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>技能：移动</t>
+          <t>技能：死亡</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ability.Attack</t>
+          <t>Ability.Move</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>技能：攻击</t>
+          <t>技能：移动</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ability.Defend</t>
+          <t>Ability.Attack</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>技能：防御</t>
+          <t>技能：攻击</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ability.Jump</t>
+          <t>Ability.Defend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>技能：跳跃</t>
+          <t>技能：防御</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ability.Dodge</t>
+          <t>Ability.Jump</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>技能：闪避</t>
+          <t>技能：跳跃</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ability.Magic</t>
+          <t>Ability.Dodge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>魔法</t>
+          <t>技能：闪避</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ability.Magic.Boom</t>
+          <t>Ability.Magic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>爆弹</t>
+          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ability.Gun</t>
+          <t>Ability.Magic.Boom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>枪械</t>
+          <t>爆弹</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>3001</v>
+        <v>2010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event.Moving</t>
+          <t>Ability.Gun</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>事件：正在移动</t>
+          <t>枪械</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Event.Dodging</t>
+          <t>Event.Moving</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>事件：正在闪避</t>
+          <t>事件：正在移动</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event.Attacking</t>
+          <t>Event.Dodging</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>事件：正在攻击</t>
+          <t>事件：正在闪避</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>4001</v>
+        <v>3003</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>State.Buff</t>
+          <t>Event.Attacking</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>状态：正向增益</t>
+          <t>事件：正在攻击</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State.Debuff</t>
+          <t>State.Buff</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>状态：负面增益</t>
+          <t>状态：正向增益</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>5001</v>
+        <v>4002</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Guide.Type1</t>
+          <t>State.Debuff</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>新手引导：类型1</t>
+          <t>状态：负面增益</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Guide.Type2</t>
+          <t>Guide.Type1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>新手引导：类型2</t>
+          <t>新手引导：类型1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Guide.Type3</t>
+          <t>Guide.Type2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>新手引导：类型3</t>
+          <t>新手引导：类型2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1000000</v>
+        <v>5003</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faction</t>
+          <t>Guide.Type3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>阵营描述标签</t>
+          <t>新手引导：类型3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>2010001</v>
+        <v>6001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ability.Gun.Aim</t>
+          <t>Cooldown.Dodge</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>瞄准</t>
+          <t>冷却：闪避</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>2010002</v>
+        <v>1000000</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ability.Gun.Shoot</t>
+          <t>Faction</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>阵营描述标签</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>2010003</v>
+        <v>2010001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ability.Gun.SuperShoot</t>
+          <t>Ability.Gun.Aim</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>强力射击</t>
+          <t>瞄准</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>4001001</v>
+        <v>2010002</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>State.Buff.BulkUp</t>
+          <t>Ability.Gun.Shoot</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>霸体</t>
+          <t>射击</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>4001002</v>
+        <v>2010003</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>State.Buff.SpeedUp</t>
+          <t>Ability.Gun.SuperShoot</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>状态：移速增加</t>
+          <t>强力射击</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
+        <v>4001001</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>State.Buff.BulkUp</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>霸体</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>4001002</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>State.Buff.SpeedUp</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>状态：移速增加</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
         <v>4001003</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>State.Buff.SpCosting</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>状态：耐力消耗中</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>4001004</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>State.Buff.Invincible</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>状态：无敌</t>
         </is>
       </c>
     </row>
